--- a/data/Event_Data_NNA07VR-104.xlsx
+++ b/data/Event_Data_NNA07VR-104.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>15-09-2569 20:50</t>
+          <t>14-10-2569 06:41</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -468,14 +468,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>13-09-2569 06:18</t>
+          <t>15-09-2569 20:50</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -490,14 +490,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12-09-2569 23:02</t>
+          <t>13-09-2569 06:18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,7 +519,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>09-09-2569 05:03</t>
+          <t>12-09-2569 23:02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -534,14 +534,14 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>06-09-2569 22:54</t>
+          <t>09-09-2569 05:03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -563,7 +563,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>06-09-2569 14:32</t>
+          <t>06-09-2569 22:54</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,7 +585,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>05-09-2569 12:01</t>
+          <t>06-09-2569 14:32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>30-08-2569 12:21</t>
+          <t>05-09-2569 12:01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -622,14 +622,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>29-08-2569 00:49</t>
+          <t>30-08-2569 12:21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -644,14 +644,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>27-08-2569 20:39</t>
+          <t>29-08-2569 00:49</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -666,14 +666,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>27-08-2569 14:46</t>
+          <t>27-08-2569 20:39</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -688,14 +688,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26-08-2569 15:23</t>
+          <t>27-08-2569 14:46</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -717,7 +717,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>25-08-2569 20:22</t>
+          <t>26-08-2569 15:23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>25-08-2569 06:15</t>
+          <t>25-08-2569 20:22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>22-08-2569 13:12</t>
+          <t>25-08-2569 06:15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -776,14 +776,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20-08-2569 15:09</t>
+          <t>22-08-2569 13:12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -793,19 +793,19 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.17</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>17-08-2569 07:39</t>
+          <t>20-08-2569 15:09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -815,19 +815,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 15.17</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16-08-2569 19:03</t>
+          <t>17-08-2569 07:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -849,7 +849,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08-08-2569 12:56</t>
+          <t>16-08-2569 19:03</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -864,14 +864,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>30-07-2569 15:39</t>
+          <t>08-08-2569 12:56</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -881,19 +881,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 16.44</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20-07-2569 07:33</t>
+          <t>30-07-2569 15:39</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -908,14 +908,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 08.17</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 16.44</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19-07-2569 06:36</t>
+          <t>20-07-2569 07:33</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -925,19 +925,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 08.17</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>18-07-2569 06:49</t>
+          <t>19-07-2569 06:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -952,14 +952,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>17-07-2569 20:17</t>
+          <t>18-07-2569 06:49</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>16-07-2569 07:58</t>
+          <t>17-07-2569 20:17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -991,19 +991,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>T/L เถาวัลย์ขึ้นระบบจำหน่าย สาย 50ACSR บ้านม่วง ห่าง R = 3 กม.</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>11-07-2569 03:22</t>
+          <t>16-07-2569 07:58</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1018,14 +1018,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 04.28</t>
+          <t>T/L เถาวัลย์ขึ้นระบบจำหน่าย สาย 50ACSR บ้านม่วง ห่าง R = 3 กม.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08-07-2569 13:18</t>
+          <t>11-07-2569 03:22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1035,19 +1035,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 04.28</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>30-06-2569 14:57</t>
+          <t>08-07-2569 13:18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1062,14 +1062,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>30-06-2569 06:35</t>
+          <t>30-06-2569 14:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1091,7 +1091,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>27-06-2569 08:35</t>
+          <t>30-06-2569 06:35</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>27-06-2569 05:15</t>
+          <t>27-06-2569 08:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1128,14 +1128,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26-06-2569 00:11</t>
+          <t>27-06-2569 05:15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1150,14 +1150,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>22-06-2569 14:10</t>
+          <t>26-06-2569 00:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1172,14 +1172,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>18-06-2569 06:48</t>
+          <t>22-06-2569 14:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1194,14 +1194,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08-06-2569 03:07</t>
+          <t>18-06-2569 06:48</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1216,14 +1216,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05-06-2569 05:16</t>
+          <t>08-06-2569 03:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1238,14 +1238,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>03-06-2569 00:15</t>
+          <t>05-06-2569 05:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>01-06-2569 05:21</t>
+          <t>03-06-2569 00:15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1289,7 +1289,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>31-05-2569 02:28</t>
+          <t>01-06-2569 05:21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1299,19 +1299,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 03.45</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>30-05-2569 21:20</t>
+          <t>31-05-2569 02:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1326,14 +1326,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>T/L ลูกถ้วยแรงสูงชำรุด เฟส B สาย 50 A บ้านม่วง ห่าง R = 18 กม. จ่ายไฟ 22.51</t>
+          <t>T/L ไม่พบสาเหตุ จ่ายไฟ 03.45</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29-05-2569 02:32</t>
+          <t>30-05-2569 21:20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1343,19 +1343,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
+          <t>T/L ลูกถ้วยแรงสูงชำรุด เฟส B สาย 50 A บ้านม่วง ห่าง R = 18 กม. จ่ายไฟ 22.51</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>28-05-2569 19:48</t>
+          <t>29-05-2569 02:32</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1365,19 +1365,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> T/L สายแรงสูง 120A ขาดเฟส C บ้านม่วง หลัง NNA07VR-104 </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ   </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>28-05-2569 18:58</t>
+          <t>28-05-2569 19:48</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1387,19 +1387,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t xml:space="preserve"> T/L สายแรงสูง 120A ขาดเฟส C บ้านม่วง หลัง NNA07VR-104 </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>28-05-2569 18:36</t>
+          <t>28-05-2569 18:58</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1409,19 +1409,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>T/L ไม่พบสาเหตุ (ขณะ Manual)</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26-05-2569 17:48</t>
+          <t>28-05-2569 18:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1431,19 +1431,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>T/R</t>
+          <t>T/L</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t>T/L ไม่พบสาเหตุ (ขณะ Manual)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25-05-2569 02:50</t>
+          <t>26-05-2569 17:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1465,7 +1465,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>24-05-2569 15:15</t>
+          <t>25-05-2569 02:50</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1480,14 +1480,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>24-05-2569 10:12</t>
+          <t>24-05-2569 15:15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1509,7 +1509,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>21-05-2569 14:27</t>
+          <t>24-05-2569 10:12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1524,14 +1524,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>21-05-2569 06:40</t>
+          <t>21-05-2569 14:27</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1546,14 +1546,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20-05-2569 03:55</t>
+          <t>21-05-2569 06:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1568,14 +1568,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>18-05-2569 18:22</t>
+          <t>20-05-2569 03:55</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1590,14 +1590,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>T/R ไม่ทราบสาเหตุ</t>
+          <t xml:space="preserve">T/R ไม่ทราบสาเหตุ  </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>19-04-2569 09:49</t>
+          <t>18-05-2569 18:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1607,19 +1607,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>T/L</t>
+          <t>T/R</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>T/L กิ่งไม้หักพาดสายแรงสูง 50 ACSR บ้านวังสิม ห่าง R = 18 กม. จ่ายไฟ 10.44</t>
+          <t>T/R ไม่ทราบสาเหตุ</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23-03-2569 06:20</t>
+          <t>19-04-2569 09:49</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1634,27 +1634,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>T/L ต้นไม้หักพาดสาย 185 A เฟส ABC บ.โคกสูง ห่าง R9กม.จ่ายไฟ 07.32</t>
+          <t>T/L กิ่งไม้หักพาดสายแรงสูง 50 ACSR บ้านวังสิม ห่าง R = 18 กม. จ่ายไฟ 10.44</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>23-03-2569 06:20</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NNA07VR-104</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>T/L</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>T/L ต้นไม้หักพาดสาย 185 A เฟส ABC บ.โคกสูง ห่าง R9กม.จ่ายไฟ 07.32</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
           <t>25-02-2569 04:23</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NNA07VR-104</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NNA07VR-104</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
         <is>
           <t>T/L</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>T/L ก่อไผ่หักพาดสาย50 ACSR ห่าง R.5กม. จ่ายไฟ 05.31</t>
         </is>
